--- a/Result/profitability/1519.xlsx
+++ b/Result/profitability/1519.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5275</v>
+        <v>3.39625</v>
       </c>
       <c r="N2" t="n">
-        <v>37.78625</v>
+        <v>38.43375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.9</v>
       </c>
       <c r="M3" t="n">
-        <v>3.105</v>
+        <v>2.8275</v>
       </c>
       <c r="N3" t="n">
-        <v>35.805</v>
+        <v>36.69</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.88</v>
       </c>
       <c r="M4" t="n">
-        <v>2.53375</v>
+        <v>2.5625</v>
       </c>
       <c r="N4" t="n">
-        <v>34.15625</v>
+        <v>35.1125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.63</v>
       </c>
       <c r="M5" t="n">
-        <v>2.2375</v>
+        <v>2.32875</v>
       </c>
       <c r="N5" t="n">
-        <v>32.06375</v>
+        <v>32.455</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.65</v>
       </c>
       <c r="M6" t="n">
-        <v>2.00625</v>
+        <v>1.97875</v>
       </c>
       <c r="N6" t="n">
-        <v>30.16</v>
+        <v>30.38625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5925</v>
+        <v>1.3325</v>
       </c>
       <c r="N7" t="n">
-        <v>26.785</v>
+        <v>26.9475</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.87</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0375</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>24.6275</v>
+        <v>24.61375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.15</v>
       </c>
       <c r="M9" t="n">
-        <v>0.645</v>
+        <v>0.6449999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>20.88875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5456</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3082</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2373</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1206</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>22.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>82</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1288</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1021</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.81375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>40.245</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.06000000000000005</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.01823708206686936</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1099999999999994</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.002522357257509711</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.130000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07753282140203122</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
